--- a/literature-review/Paper Dictionary.xlsx
+++ b/literature-review/Paper Dictionary.xlsx
@@ -62,7 +62,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -76,11 +76,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -94,6 +122,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -477,6 +507,12 @@
           <t>Long-Lecture Video RAG Benchmark</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="6" t="n"/>
     </row>
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
@@ -1114,6 +1150,369 @@
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Video-RAG: Visually-aligned Retrieval-Augmented Long Video Comprehension</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2411.13093</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Training-free pipeline that extracts visually-aligned auxiliary texts (OCR, audio, object detection) from video and injects them alongside frames into any LVLM. Achieves SOTA on Video-MME, MLVU, and LongVideoBench, surpassing Gemini-1.5-Pro with a 72B open model.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Plug-and-play with any existing LVLM; uses multi-modal signal extraction (audio, OCR, object detection); no retraining required; strong benchmark results.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Single-turn retrieval limits multi-hop temporal reasoning; relies on external extraction tools; not evaluated on educational lecture videos or transcript-based chunking.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>VideoRAG: Retrieval-Augmented Generation over Video Corpus</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2501.05874</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>First RAG framework that dynamically retrieves relevant videos from a large corpus using LVLMs for both representation and generation. Includes a frame selection mechanism and subtitle extraction fallback when captions are unavailable.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Corpus-level video retrieval (not single-video QA); direct multimodal processing without text conversion; flexible subtitle fallback strategy.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Targets corpus retrieval rather than temporal span grounding within long videos; no temporal IoU evaluation; not applied to educational lecture domain.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>VideoRAG: Retrieval-Augmented Generation with Extreme Long-Context Videos</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2502.01549</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Dual-channel architecture combining graph-based textual knowledge grounding with multi-modal context encoding, enabling RAG over unlimited-length videos. Evaluated on LongerVideos benchmark (160 videos, 134+ hours) including lecture, documentary, and entertainment content.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Handles unlimited video length; cross-video knowledge graphs capture semantic relationships; LongerVideos benchmark includes lectures; accepted at KDD 2026.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Complex graph construction overhead; no explicit per-hop temporal grounding; knowledge graph quality depends on LLM extraction accuracy.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>E-VRAG: Enhancing Long Video Understanding with Resource-Efficient Retrieval Augmented Generation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.01546</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Frame pre-filtering via hierarchical query decomposition eliminates irrelevant frames; lightweight VLM scores remaining frames; global inter-frame score distribution guides final retrieval. Reduces computation 70% versus baselines without training.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Significant computational efficiency gains; training-free; strong results on four public benchmarks including Video-MME.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Frame-level retrieval may miss transcript-only information; lightweight VLM scoring may degrade on domain-specific technical content; not tested on educational lectures.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Long Video Understanding with Learnable Retrieval in Video-Language Models</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.04931</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R-VLM selects the K most relevant video chunks given a query, using visual tokens from those chunks as LLM context. Reduces token count, eliminates noise, and provides interpretable chunk-level justifications for where answers were found.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Simple and effective; chunk-based retrieval is interpretable; strong zero-shot generalization across multiple VideoQA datasets.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>No temporal span precision (chunk-level only); does not incorporate transcript/audio signals; not evaluated on long educational lectures; predates modern RAG paradigms.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Enhancing Question Answering in Lecture Videos with a Multimodal Retrieval-Augmented Generation Framework</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/chapter/10.1007/978-3-031-81542-3_15</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>RAG system specifically designed for lecture video QA, combining audio transcript retrieval with slide image text extraction. Users query a video corpus and receive answers with pointers to the most relevant video segments.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Domain-specific design for lecture videos (closest paper to this project); combines audio and visual text modalities; corpus-level QA with segment retrieval.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>No temporal grounding evaluation metrics (temporal IoU, hit rate); single-hop QA only; no comparison between retrieval configurations (transcript-only vs. multimodal).</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Video Enriched Retrieval Augmented Generation Using Aligned Video Captions</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.17706</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Proposes 'aligned visual captions' describing both visual and audio content as a text-only bridge for integrating videos into RAG pipelines. Requires less context window space than raw frame sampling and is compatible with text-based retrieval stacks.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Text-based integration avoids multimodal token overhead; curates evaluation dataset with automatic evaluation procedures; directly applicable to transcript+caption RAG pipelines.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Caption quality is upper-bounded by the captioning model; temporal resolution limited by caption density; not evaluated on educational lecture videos specifically.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Narrative Aligned Long Form Video Question Answering</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.19481</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Introduces NA-VQA, a benchmark of 88 full-length movies with 4,400 QA pairs targeting narrative reasoning — tracking character intentions, connecting distant events, and reconstructing causal chains across an entire film. Proposes Video-NaRA, a framework that builds event-level chains stored in structured memory for retrieval during reasoning, achieving up to 3% improvement over leading MLLMs on complex narrative questions.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>First benchmark explicitly focused on long-range multi-hop causal reasoning in full-length video; event-chain memory is a novel retrieval structure beyond flat vector search; reveals that SOTA MLLMs fail on distant-evidence questions; dataset to be released.</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Movie/narrative domain is fundamentally different from educational lecture content — reasoning requires character tracking, not concept-building; no temporal IoU evaluation; no comparison of retrieval configurations (transcript-only vs. multimodal); no per-hop ground truth span annotations; structured event chains are hand-crafted rather than derived from a retrieval pipeline.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>LongVidSearch: An Agentic Benchmark for Multi-hop Evidence Retrieval Planning in Long Videos</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.14468</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Introduces a benchmark of 3,000 questions across 447 long videos (avg 26 min) that enforces strict multi-hop evidence retrieval with 2-hop, 3-hop, and 4-hop configurations — removing any single clip makes the question unsolvable. Evaluates AI agents on iterative retrieval planning across four reasoning categories (State Mutation, Causal Inference, Global Summary, Visual Tracking); even GPT-5 achieves only 42.43% accuracy, identifying retrieval planning as the primary bottleneck.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>First benchmark to enforce strict per-hop retrieval necessity with explicit hop counts; agentic evaluation interface exposes planning failures invisible to single-pass models; broad reasoning categories; strong evidence that multi-hop retrieval is unsolved even for GPT-5.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>General video content (not educational lectures); uses agentic tool-call retrieval rather than a transcript-chunk RAG pipeline; evaluates answer accuracy only — no temporal IoU or hit rate@k; no transcript or audio modality; no comparison of retrieval configurations; no per-hop ground truth time spans provided to the evaluator.</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>EduVidQA: Generating and Evaluating Long-form Answers to Student Questions based on Lecture Videos</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.24120</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Presents EduVidQA, a dataset of 5,252 QA pairs from 296 CS lecture videos (ML, Algorithms, NLP, Deep Learning) spanning Bloom's taxonomy difficulty levels; includes timestamps for all questions and flags ~44% as visually dependent. Benchmarks six SOTA MLLMs, showing the task remains significantly challenging for current systems.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closest domain match to this project (CS lecture videos, technical content); timestamps included; Bloom's taxonomy difficulty tagging; visual dependence flagging; real student questions used for 270 manually curated pairs.</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>No RAG pipeline — uses a fixed 4-minute context window around each timestamp; no multi-hop questions or per-hop span annotations; no temporal IoU or hit rate@k evaluation; QA pairs are mostly synthetically generated (only 270/5252 manually curated); no comparison of retrieval configurations.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Vgent: Graph-based Retrieval-Reasoning-Augmented Generation For Long Video Understanding</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2510.14032</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Proposes Vgent (NeurIPS 2025 Spotlight), a framework that represents video content as semantic relationship graphs over clips and adds an intermediate structured verification step to reduce retrieval noise in LVLMs. Achieves 3.0–5.4% improvement on MLVU and outperforms existing video RAG methods by 8.6%.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Graph-based semantic structure captures relationships between clips beyond cosine similarity; structured verification reduces hallucination from noisy retrieval; NeurIPS 2025 Spotlight recognition; strong empirical gains over flat video RAG baselines.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated on general video benchmarks (MLVU, not lecture domain); no temporal IoU evaluation; no multi-hop per-hop annotation; graph construction requires additional preprocessing overhead; no comparison of text-only vs. multimodal retrieval configurations.</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/literature-review/Paper Dictionary.xlsx
+++ b/literature-review/Paper Dictionary.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +62,26 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -124,6 +147,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -499,6 +537,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -551,6 +590,11 @@
           <t>Open Research Directions</t>
         </is>
       </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Venue / Peer-Reviewed?</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -584,6 +628,11 @@
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -617,6 +666,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -646,6 +700,11 @@
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -675,6 +734,11 @@
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -704,6 +768,11 @@
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -733,6 +802,11 @@
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -766,6 +840,11 @@
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>✓ WACV 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -795,6 +874,11 @@
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -828,6 +912,11 @@
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2020</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -861,6 +950,11 @@
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -890,6 +984,11 @@
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -923,6 +1022,11 @@
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓ ICML 2023</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -956,6 +1060,11 @@
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓ National Science Review (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -989,6 +1098,11 @@
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>✓ Interspeech 2023</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1022,6 +1136,11 @@
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>✓ Interspeech 2024</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1055,6 +1174,11 @@
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — paywalled, verify</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -1088,6 +1212,11 @@
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>~ RANLP 2021 Workshop (SRW) (workshop — peer-reviewed)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1121,6 +1250,11 @@
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>✓ MDPI Sensors (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1150,6 +1284,11 @@
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — no URL, verify</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1183,6 +1322,11 @@
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1216,6 +1360,11 @@
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>✓ ACL Findings 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1249,6 +1398,11 @@
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1282,6 +1436,11 @@
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1315,6 +1474,11 @@
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE Transactions on Multimedia (TMM)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -1348,6 +1512,11 @@
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>✓ Springer LNCS conference chapter (peer-reviewed — specific conference, verify)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1381,6 +1550,11 @@
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>~ SIGIR 2024 Workshop (MRR) (workshop — peer-reviewed)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -1414,6 +1588,11 @@
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1447,6 +1626,11 @@
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -1480,6 +1664,11 @@
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1513,6 +1702,11 @@
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2025 (Spotlight)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/literature-review/Paper Dictionary.xlsx
+++ b/literature-review/Paper Dictionary.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +82,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -160,6 +165,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -678,7 +686,11 @@
           <t>MovieChat+: Question-Aware Sparse Memory for Long Video Question Answering</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2404.17176</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>MovieChat+ proposes a question-aware sparse memory mechanism for long video QA, selectively compressing video tokens to handle hour-long content without prohibitive memory costs. It demonstrates improved performance over dense-memory baselines on long-video benchmarks.</t>
@@ -700,9 +712,9 @@
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE TPAMI 2026 (Transactions on Pattern Analysis and Machine Intelligence)</t>
         </is>
       </c>
     </row>
@@ -712,7 +724,11 @@
           <t>VideoABC: A Real-World Video Dataset for Abductive Visual Reasoning</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/9893026/</t>
+        </is>
+      </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>VideoABC introduces abductive visual reasoning over instructional videos, requiring models to infer the most plausible explanation for observations across long-term temporal sequences. It uses real-world instructional content, making it closer to lecture settings than typical entertainment video datasets.</t>
@@ -734,9 +750,9 @@
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE TIP 2022 (Transactions on Image Processing)</t>
         </is>
       </c>
     </row>
@@ -746,7 +762,11 @@
           <t>Dual-level Dynamic Heterogeneous Graph Network for Video Question Answering</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/abs/pii/S0893608025009748</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Proposes a dual-level graph network to model entity and event relationships in video QA, addressing the tendency of VLMs to rely on language shortcuts rather than visual grounding. Introduces richer entity/event annotations to improve multi-modal reasoning.</t>
@@ -768,9 +788,9 @@
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>✓ Neural Networks, Elsevier (2025)</t>
         </is>
       </c>
     </row>
@@ -780,7 +800,11 @@
           <t>Temporal Sentence Grounding in Videos: A Survey and Future Directions</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2201.08071</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>A comprehensive survey of temporal sentence grounding in videos (TSGV), also known as natural language video localization and video moment retrieval. Covers foundational datasets, evaluation metrics including temporal IoU, and model architectures from proposal-based to proposal-free methods.</t>
@@ -802,9 +826,9 @@
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE TPAMI 2023 (Transactions on Pattern Analysis and Machine Intelligence)</t>
         </is>
       </c>
     </row>
@@ -852,7 +876,11 @@
           <t>Caption Assisted Multimodal Large Language Model for Video Moment Retrieval</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11206011</t>
+        </is>
+      </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t>CALCE proposes a two-stage coarse-to-fine framework for video moment retrieval using frame captions to assist multimodal LLMs. Frame captions bridge the gap between visual and textual modalities, improving temporal localization accuracy.</t>
@@ -874,9 +902,9 @@
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>✓ IEEE TIP 2025 — NOTE: same paper as row 22 (CALCE) — possible duplicate entry</t>
         </is>
       </c>
     </row>
@@ -962,7 +990,11 @@
           <t>Retrieval Augmented Generation for Large Language Models in Healthcare: A Systematic Review</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.plos.org/digitalhealth/article?id=10.1371/journal.pdig.0000877</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Surveys RAG applications in healthcare, highlighting common failure modes including hallucination, retrieval errors, and citation inaccuracy. Provides a framework for evaluating RAG reliability in high-stakes domains, with metrics applicable to educational QA evaluation.</t>
@@ -984,9 +1016,9 @@
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>✓ PLOS Digital Health (2025)</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1294,11 @@
           <t>Caption Assisted Multimodal LLM from Coarse to Fine (CALCE) for Video Moment Retrieval</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/document/11206011</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>A two-stage coarse-to-fine retrieval framework where frame captions assist MLLMs in localizing specific video moments. The coarse stage narrows candidate segments; the fine stage reranks using multimodal reasoning.</t>
@@ -1284,9 +1320,9 @@
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — no URL, verify</t>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>✓ IEEE TIP 2025 — NOTE: same paper as row 11 (Caption Assisted LLM) — possible duplicate entry</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1550,7 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>✓ Springer LNCS conference chapter (peer-reviewed — specific conference, verify)</t>
+          <t>✓ AIMSA 2024 (19th Intl. Conf. on AI: Methodology, Systems, and Applications), Springer LNCS</t>
         </is>
       </c>
     </row>

--- a/literature-review/Paper Dictionary.xlsx
+++ b/literature-review/Paper Dictionary.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -871,569 +871,569 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Caption Assisted Multimodal Large Language Model for Video Moment Retrieval</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Retrieval-Augmented Generation for Knowledge-Intensive NLP Tasks</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2005.11401v4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>The foundational RAG paper combining dense passage retrieval (DPR) with a seq2seq generator for open-domain QA. Introduces the RAG-Token and RAG-Sequence variants and demonstrates that retrieval-augmented models outperform parametric-only LLMs on knowledge-intensive tasks.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Foundational methodology for this entire project; establishes the retrieve-then-generate paradigm with grounded answers.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Designed for text-only, short-document retrieval; does not address temporal metadata, video content, or citation formatting with timestamps.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Engineering the RAG Stack: A Comprehensive Review of the Architecture and Trust Frameworks for Retrieval-Augmented Generation Systems</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.05264v1</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A systematic review of RAG architectures and trust frameworks from 2018 to 2025, covering embedding models, vector databases, chunking strategies, retrieval algorithms, and deployment practices. Provides practical guidance for building production-grade RAG systems.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Comprehensive coverage of chunking strategies and embedding model selection — directly informs design decisions in this project (chunk size, overlap, embedding model choice).</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Focuses on text-only RAG over structured documents; does not address video transcripts, timestamp metadata, or multimodal retrieval.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Retrieval Augmented Generation for Large Language Models in Healthcare: A Systematic Review</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.plos.org/digitalhealth/article?id=10.1371/journal.pdig.0000877</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Surveys RAG applications in healthcare, highlighting common failure modes including hallucination, retrieval errors, and citation inaccuracy. Provides a framework for evaluating RAG reliability in high-stakes domains, with metrics applicable to educational QA evaluation.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Detailed failure mode taxonomy useful for the failure modes section of the project report; citation accuracy evaluation framework is directly applicable.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare domain focus; text-only RAG without temporal or video modalities.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>✓ PLOS Digital Health (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>BLIP-2: Bootstrapping Language-Image Pre-training with Frozen Image Encoders and Large Language Models</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/pdf/2301.12597</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>BLIP-2 introduces a Querying Transformer (Q-Former) that bridges frozen image encoders and LLMs for efficient vision-language pre-training. It can generate detailed image captions from video keyframes without task-specific fine-tuning, making it a strong candidate for the frame captioning component.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>State-of-the-art image captioning with no fine-tuning required; Q-Former architecture is compute-efficient; supports lecture slide and whiteboard captioning.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Designed for static images rather than video understanding; captions individual frames without temporal context between frames.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>✓ ICML 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>A Survey on Multimodal Large Language Models</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.13549v4</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive survey of multimodal LLMs (MLLMs) including GPT-4V, covering architectures for combining visual encoders with LLMs, instruction tuning, and evaluation. Contextualizes the role of frame-level visual understanding in video QA pipelines.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Broad coverage of visual encoding strategies relevant to frame captioning; covers evaluation benchmarks that provide context for this project's metrics.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Survey focus rather than specific method; does not address video-specific temporal reasoning or retrieval.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓ National Science Review (2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Whisper-AT: Noise-Robust Automatic Speech Recognizers are Also Strong General Audio Event Taggers</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2307.03183v1</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Analyzes Whisper's internal audio representations and demonstrates that its features, while trained for ASR, are highly correlated with non-speech sounds. Extends Whisper to audio event tagging, providing insights into the model's robustness properties relevant to lecture transcription.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Provides detailed analysis of Whisper's noise robustness — directly relevant to transcribing lecture audio with background noise, audience questions, and slide-change sounds.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Focuses on audio tagging rather than transcript quality or word-level timestamp accuracy; does not evaluate on lecture-specific audio.</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓ Interspeech 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Whisper-Flamingo: Integrating Visual Features into Whisper for Audio-Visual Speech Recognition and Translation</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.10082v3</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Extends Whisper with visual (lip-reading) features using a Flamingo-style cross-attention approach for audio-visual speech recognition. Demonstrates improved robustness in noisy environments by leveraging both audio and visual cues.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Shows that visual features can complement Whisper's ASR quality — relevant to future work on using visual slides to improve lecture transcription accuracy.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Requires synchronized lip-video input not available in standard lecture recordings; adds significant computational overhead.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>✓ Interspeech 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Real-Time Question Generation from Educational Video Lectures using Deep Learning</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>[PAYWALLED]https://www.semanticscholar.org/paper/760f162a3f2313418e747b333783e65a4ced995d</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Proposes a pipeline for real-time question generation from live lecture audio using Whisper for transcription and Flan-T5 for question generation. Most directly related to this project's QA generation component, combining ASR with QA generation in an educational setting.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Combines Whisper transcription with LLM-based question generation — same technical stack as this project; educational lecture domain.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>No temporal span annotation or retrieval evaluation; generated questions are not validated for benchmark quality; no vector database or RAG component.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Unknown — paywalled, verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Generating Answer Candidates for Quizzes and Answer-Aware Question Generators</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2108.12898v1</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Addresses automatic quiz question generation including distractor generation for multiple-choice format, relevant to ensuring QA quality and diversity in this benchmark. Proposes answer-aware question generation that conditions on the answer span — analogous to this project's chunk-conditioned QA generation.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Answer-aware generation approach is directly analogous to generating questions from specific transcript chunks; addresses answer candidate quality.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Text-only (not video); does not address temporal grounding or transcript-based QA; no retrieval evaluation.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>~ RANLP 2021 Workshop (SRW) (workshop — peer-reviewed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Cross-Modal Transformer-Based Streaming Dense Video Captioning with Neural ODE Temporal Localization</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s25030707</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Proposes CMSTR-ODE for dense video captioning with precise temporal localization using Neural ODEs, addressing event boundary detection in complex multi-event videos. The temporal localization component is relevant to aligning frame captions with transcript chunks in this project.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Streaming (real-time capable) dense captioning with precise temporal boundaries; handles multi-event videos similar to long lectures.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Captioning rather than QA; neural ODE approach is computationally expensive; not evaluated on educational content.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>✓ MDPI Sensors (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Caption Assisted Multimodal LLM from Coarse to Fine (CALCE) for Video Moment Retrieval</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>https://ieeexplore.ieee.org/document/11206011</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CALCE proposes a two-stage coarse-to-fine framework for video moment retrieval using frame captions to assist multimodal LLMs. Frame captions bridge the gap between visual and textual modalities, improving temporal localization accuracy.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>A two-stage coarse-to-fine retrieval framework where frame captions assist MLLMs in localizing specific video moments. The coarse stage narrows candidate segments; the fine stage reranks using multimodal reasoning.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Demonstrates the value of frame captions for temporal retrieval, directly supporting the transcript-plus-frame-caption retrieval configuration in this project.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>End-to-end retrieval model rather than RAG pipeline; does not use a vector database or support citation generation.</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>✓ IEEE TIP 2025 — NOTE: same paper as row 22 (CALCE) — possible duplicate entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Retrieval-Augmented Generation for Knowledge-Intensive NLP Tasks</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2005.11401v4</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>The foundational RAG paper combining dense passage retrieval (DPR) with a seq2seq generator for open-domain QA. Introduces the RAG-Token and RAG-Sequence variants and demonstrates that retrieval-augmented models outperform parametric-only LLMs on knowledge-intensive tasks.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2020-05-22</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Foundational methodology for this entire project; establishes the retrieve-then-generate paradigm with grounded answers.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Designed for text-only, short-document retrieval; does not address temporal metadata, video content, or citation formatting with timestamps.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>✓ NeurIPS 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Engineering the RAG Stack: A Comprehensive Review of the Architecture and Trust Frameworks for Retrieval-Augmented Generation Systems</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2601.05264v1</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>A systematic review of RAG architectures and trust frameworks from 2018 to 2025, covering embedding models, vector databases, chunking strategies, retrieval algorithms, and deployment practices. Provides practical guidance for building production-grade RAG systems.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Comprehensive coverage of chunking strategies and embedding model selection — directly informs design decisions in this project (chunk size, overlap, embedding model choice).</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Focuses on text-only RAG over structured documents; does not address video transcripts, timestamp metadata, or multimodal retrieval.</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Directly validates the frame-caption-augmented retrieval hypothesis central to this project's second configuration.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Requires end-to-end MLLM inference rather than lightweight vector DB retrieval; not adapted for lecture-domain temporal grounding.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE TIP 2025 (Transactions on Image Processing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Video-RAG: Visually-aligned Retrieval-Augmented Long Video Comprehension</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2411.13093</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Training-free pipeline that extracts visually-aligned auxiliary texts (OCR, audio, object detection) from video and injects them alongside frames into any LVLM. Achieves SOTA on Video-MME, MLVU, and LongVideoBench, surpassing Gemini-1.5-Pro with a 72B open model.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Plug-and-play with any existing LVLM; uses multi-modal signal extraction (audio, OCR, object detection); no retraining required; strong benchmark results.</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Single-turn retrieval limits multi-hop temporal reasoning; relies on external extraction tools; not evaluated on educational lecture videos or transcript-based chunking.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>VideoRAG: Retrieval-Augmented Generation over Video Corpus</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2501.05874</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>First RAG framework that dynamically retrieves relevant videos from a large corpus using LVLMs for both representation and generation. Includes a frame selection mechanism and subtitle extraction fallback when captions are unavailable.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Corpus-level video retrieval (not single-video QA); direct multimodal processing without text conversion; flexible subtitle fallback strategy.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Targets corpus retrieval rather than temporal span grounding within long videos; no temporal IoU evaluation; not applied to educational lecture domain.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>✓ ACL Findings 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>VideoRAG: Retrieval-Augmented Generation with Extreme Long-Context Videos</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2502.01549</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Dual-channel architecture combining graph-based textual knowledge grounding with multi-modal context encoding, enabling RAG over unlimited-length videos. Evaluated on LongerVideos benchmark (160 videos, 134+ hours) including lecture, documentary, and entertainment content.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Handles unlimited video length; cross-video knowledge graphs capture semantic relationships; LongerVideos benchmark includes lectures; accepted at KDD 2026.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Complex graph construction overhead; no explicit per-hop temporal grounding; knowledge graph quality depends on LLM extraction accuracy.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Retrieval Augmented Generation for Large Language Models in Healthcare: A Systematic Review</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>https://journals.plos.org/digitalhealth/article?id=10.1371/journal.pdig.0000877</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Surveys RAG applications in healthcare, highlighting common failure modes including hallucination, retrieval errors, and citation inaccuracy. Provides a framework for evaluating RAG reliability in high-stakes domains, with metrics applicable to educational QA evaluation.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Detailed failure mode taxonomy useful for the failure modes section of the project report; citation accuracy evaluation framework is directly applicable.</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare domain focus; text-only RAG without temporal or video modalities.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>✓ PLOS Digital Health (2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>BLIP-2: Bootstrapping Language-Image Pre-training with Frozen Image Encoders and Large Language Models</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>http://arxiv.org/pdf/2301.12597</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>BLIP-2 introduces a Querying Transformer (Q-Former) that bridges frozen image encoders and LLMs for efficient vision-language pre-training. It can generate detailed image captions from video keyframes without task-specific fine-tuning, making it a strong candidate for the frame captioning component.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>State-of-the-art image captioning with no fine-tuning required; Q-Former architecture is compute-efficient; supports lecture slide and whiteboard captioning.</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Designed for static images rather than video understanding; captions individual frames without temporal context between frames.</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>✓ ICML 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>A Survey on Multimodal Large Language Models</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2306.13549v4</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Comprehensive survey of multimodal LLMs (MLLMs) including GPT-4V, covering architectures for combining visual encoders with LLMs, instruction tuning, and evaluation. Contextualizes the role of frame-level visual understanding in video QA pipelines.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Broad coverage of visual encoding strategies relevant to frame captioning; covers evaluation benchmarks that provide context for this project's metrics.</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Survey focus rather than specific method; does not address video-specific temporal reasoning or retrieval.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>✓ National Science Review (2024)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Whisper-AT: Noise-Robust Automatic Speech Recognizers are Also Strong General Audio Event Taggers</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2307.03183v1</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Analyzes Whisper's internal audio representations and demonstrates that its features, while trained for ASR, are highly correlated with non-speech sounds. Extends Whisper to audio event tagging, providing insights into the model's robustness properties relevant to lecture transcription.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Provides detailed analysis of Whisper's noise robustness — directly relevant to transcribing lecture audio with background noise, audience questions, and slide-change sounds.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Focuses on audio tagging rather than transcript quality or word-level timestamp accuracy; does not evaluate on lecture-specific audio.</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>✓ Interspeech 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Whisper-Flamingo: Integrating Visual Features into Whisper for Audio-Visual Speech Recognition and Translation</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2406.10082v3</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Extends Whisper with visual (lip-reading) features using a Flamingo-style cross-attention approach for audio-visual speech recognition. Demonstrates improved robustness in noisy environments by leveraging both audio and visual cues.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Shows that visual features can complement Whisper's ASR quality — relevant to future work on using visual slides to improve lecture transcription accuracy.</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Requires synchronized lip-video input not available in standard lecture recordings; adds significant computational overhead.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>✓ Interspeech 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Real-Time Question Generation from Educational Video Lectures using Deep Learning</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>[PAYWALLED]https://www.semanticscholar.org/paper/760f162a3f2313418e747b333783e65a4ced995d</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Proposes a pipeline for real-time question generation from live lecture audio using Whisper for transcription and Flan-T5 for question generation. Most directly related to this project's QA generation component, combining ASR with QA generation in an educational setting.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Combines Whisper transcription with LLM-based question generation — same technical stack as this project; educational lecture domain.</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>No temporal span annotation or retrieval evaluation; generated questions are not validated for benchmark quality; no vector database or RAG component.</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Unknown — paywalled, verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Generating Answer Candidates for Quizzes and Answer-Aware Question Generators</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2108.12898v1</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Addresses automatic quiz question generation including distractor generation for multiple-choice format, relevant to ensuring QA quality and diversity in this benchmark. Proposes answer-aware question generation that conditions on the answer span — analogous to this project's chunk-conditioned QA generation.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Answer-aware generation approach is directly analogous to generating questions from specific transcript chunks; addresses answer candidate quality.</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Text-only (not video); does not address temporal grounding or transcript-based QA; no retrieval evaluation.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>~ RANLP 2021 Workshop (SRW) (workshop — peer-reviewed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Cross-Modal Transformer-Based Streaming Dense Video Captioning with Neural ODE Temporal Localization</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s25030707</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Proposes CMSTR-ODE for dense video captioning with precise temporal localization using Neural ODEs, addressing event boundary detection in complex multi-event videos. The temporal localization component is relevant to aligning frame captions with transcript chunks in this project.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Streaming (real-time capable) dense captioning with precise temporal boundaries; handles multi-event videos similar to long lectures.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Captioning rather than QA; neural ODE approach is computationally expensive; not evaluated on educational content.</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>✓ MDPI Sensors (2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Caption Assisted Multimodal LLM from Coarse to Fine (CALCE) for Video Moment Retrieval</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>https://ieeexplore.ieee.org/document/11206011</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>A two-stage coarse-to-fine retrieval framework where frame captions assist MLLMs in localizing specific video moments. The coarse stage narrows candidate segments; the fine stage reranks using multimodal reasoning.</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Directly validates the frame-caption-augmented retrieval hypothesis central to this project's second configuration.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Requires end-to-end MLLM inference rather than lightweight vector DB retrieval; not adapted for lecture-domain temporal grounding.</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>✓ IEEE TIP 2025 — NOTE: same paper as row 11 (Caption Assisted LLM) — possible duplicate entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Video-RAG: Visually-aligned Retrieval-Augmented Long Video Comprehension</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2411.13093</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Training-free pipeline that extracts visually-aligned auxiliary texts (OCR, audio, object detection) from video and injects them alongside frames into any LVLM. Achieves SOTA on Video-MME, MLVU, and LongVideoBench, surpassing Gemini-1.5-Pro with a 72B open model.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Plug-and-play with any existing LVLM; uses multi-modal signal extraction (audio, OCR, object detection); no retraining required; strong benchmark results.</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Single-turn retrieval limits multi-hop temporal reasoning; relies on external extraction tools; not evaluated on educational lecture videos or transcript-based chunking.</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>✓ NeurIPS 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>VideoRAG: Retrieval-Augmented Generation over Video Corpus</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2501.05874</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>First RAG framework that dynamically retrieves relevant videos from a large corpus using LVLMs for both representation and generation. Includes a frame selection mechanism and subtitle extraction fallback when captions are unavailable.</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Corpus-level video retrieval (not single-video QA); direct multimodal processing without text conversion; flexible subtitle fallback strategy.</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Targets corpus retrieval rather than temporal span grounding within long videos; no temporal IoU evaluation; not applied to educational lecture domain.</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>✓ ACL Findings 2025</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>VideoRAG: Retrieval-Augmented Generation with Extreme Long-Context Videos</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2502.01549</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Dual-channel architecture combining graph-based textual knowledge grounding with multi-modal context encoding, enabling RAG over unlimited-length videos. Evaluated on LongerVideos benchmark (160 videos, 134+ hours) including lecture, documentary, and entertainment content.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Handles unlimited video length; cross-video knowledge graphs capture semantic relationships; LongerVideos benchmark includes lectures; accepted at KDD 2026.</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Complex graph construction overhead; no explicit per-hop temporal grounding; knowledge graph quality depends on LLM extraction accuracy.</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>E-VRAG: Enhancing Long Video Understanding with Resource-Efficient Retrieval Augmented Generation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.01546</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Frame pre-filtering via hierarchical query decomposition eliminates irrelevant frames; lightweight VLM scores remaining frames; global inter-frame score distribution guides final retrieval. Reduces computation 70% versus baselines without training.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Significant computational efficiency gains; training-free; strong results on four public benchmarks including Video-MME.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Frame-level retrieval may miss transcript-only information; lightweight VLM scoring may degrade on domain-specific technical content; not tested on educational lectures.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr">
         <is>
           <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
@@ -1441,189 +1441,189 @@
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>E-VRAG: Enhancing Long Video Understanding with Resource-Efficient Retrieval Augmented Generation</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2508.01546</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Frame pre-filtering via hierarchical query decomposition eliminates irrelevant frames; lightweight VLM scores remaining frames; global inter-frame score distribution guides final retrieval. Reduces computation 70% versus baselines without training.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Significant computational efficiency gains; training-free; strong results on four public benchmarks including Video-MME.</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Frame-level retrieval may miss transcript-only information; lightweight VLM scoring may degrade on domain-specific technical content; not tested on educational lectures.</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Long Video Understanding with Learnable Retrieval in Video-Language Models</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.04931</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>R-VLM selects the K most relevant video chunks given a query, using visual tokens from those chunks as LLM context. Reduces token count, eliminates noise, and provides interpretable chunk-level justifications for where answers were found.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Simple and effective; chunk-based retrieval is interpretable; strong zero-shot generalization across multiple VideoQA datasets.</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>No temporal span precision (chunk-level only); does not incorporate transcript/audio signals; not evaluated on long educational lectures; predates modern RAG paradigms.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>✓ IEEE Transactions on Multimedia (TMM)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Long Video Understanding with Learnable Retrieval in Video-Language Models</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2312.04931</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>R-VLM selects the K most relevant video chunks given a query, using visual tokens from those chunks as LLM context. Reduces token count, eliminates noise, and provides interpretable chunk-level justifications for where answers were found.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Simple and effective; chunk-based retrieval is interpretable; strong zero-shot generalization across multiple VideoQA datasets.</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>No temporal span precision (chunk-level only); does not incorporate transcript/audio signals; not evaluated on long educational lectures; predates modern RAG paradigms.</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Enhancing Question Answering in Lecture Videos with a Multimodal Retrieval-Augmented Generation Framework</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/chapter/10.1007/978-3-031-81542-3_15</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>RAG system specifically designed for lecture video QA, combining audio transcript retrieval with slide image text extraction. Users query a video corpus and receive answers with pointers to the most relevant video segments.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Domain-specific design for lecture videos (closest paper to this project); combines audio and visual text modalities; corpus-level QA with segment retrieval.</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>No temporal grounding evaluation metrics (temporal IoU, hit rate); single-hop QA only; no comparison between retrieval configurations (transcript-only vs. multimodal).</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>✓ IEEE Transactions on Multimedia (TMM)</t>
+          <t>✓ AIMSA 2024 (19th Intl. Conf. on AI: Methodology, Systems, and Applications), Springer LNCS</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Enhancing Question Answering in Lecture Videos with a Multimodal Retrieval-Augmented Generation Framework</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/chapter/10.1007/978-3-031-81542-3_15</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>RAG system specifically designed for lecture video QA, combining audio transcript retrieval with slide image text extraction. Users query a video corpus and receive answers with pointers to the most relevant video segments.</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Domain-specific design for lecture videos (closest paper to this project); combines audio and visual text modalities; corpus-level QA with segment retrieval.</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>No temporal grounding evaluation metrics (temporal IoU, hit rate); single-hop QA only; no comparison between retrieval configurations (transcript-only vs. multimodal).</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>✓ AIMSA 2024 (19th Intl. Conf. on AI: Methodology, Systems, and Applications), Springer LNCS</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Video Enriched Retrieval Augmented Generation Using Aligned Video Captions</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2405.17706</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Proposes 'aligned visual captions' describing both visual and audio content as a text-only bridge for integrating videos into RAG pipelines. Requires less context window space than raw frame sampling and is compatible with text-based retrieval stacks.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Text-based integration avoids multimodal token overhead; curates evaluation dataset with automatic evaluation procedures; directly applicable to transcript+caption RAG pipelines.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Caption quality is upper-bounded by the captioning model; temporal resolution limited by caption density; not evaluated on educational lecture videos specifically.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>~ SIGIR 2024 Workshop (MRR) (workshop — peer-reviewed)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Video Enriched Retrieval Augmented Generation Using Aligned Video Captions</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2405.17706</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Proposes 'aligned visual captions' describing both visual and audio content as a text-only bridge for integrating videos into RAG pipelines. Requires less context window space than raw frame sampling and is compatible with text-based retrieval stacks.</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-27</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Text-based integration avoids multimodal token overhead; curates evaluation dataset with automatic evaluation procedures; directly applicable to transcript+caption RAG pipelines.</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Caption quality is upper-bounded by the captioning model; temporal resolution limited by caption density; not evaluated on educational lecture videos specifically.</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>~ SIGIR 2024 Workshop (MRR) (workshop — peer-reviewed)</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Narrative Aligned Long Form Video Question Answering</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.19481</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Introduces NA-VQA, a benchmark of 88 full-length movies with 4,400 QA pairs targeting narrative reasoning — tracking character intentions, connecting distant events, and reconstructing causal chains across an entire film. Proposes Video-NaRA, a framework that builds event-level chains stored in structured memory for retrieval during reasoning, achieving up to 3% improvement over leading MLLMs on complex narrative questions.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>First benchmark explicitly focused on long-range multi-hop causal reasoning in full-length video; event-chain memory is a novel retrieval structure beyond flat vector search; reveals that SOTA MLLMs fail on distant-evidence questions; dataset to be released.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Movie/narrative domain is fundamentally different from educational lecture content — reasoning requires character tracking, not concept-building; no temporal IoU evaluation; no comparison of retrieval configurations (transcript-only vs. multimodal); no per-hop ground truth span annotations; structured event chains are hand-crafted rather than derived from a retrieval pipeline.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Narrative Aligned Long Form Video Question Answering</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2603.19481</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Introduces NA-VQA, a benchmark of 88 full-length movies with 4,400 QA pairs targeting narrative reasoning — tracking character intentions, connecting distant events, and reconstructing causal chains across an entire film. Proposes Video-NaRA, a framework that builds event-level chains stored in structured memory for retrieval during reasoning, achieving up to 3% improvement over leading MLLMs on complex narrative questions.</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>First benchmark explicitly focused on long-range multi-hop causal reasoning in full-length video; event-chain memory is a novel retrieval structure beyond flat vector search; reveals that SOTA MLLMs fail on distant-evidence questions; dataset to be released.</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Movie/narrative domain is fundamentally different from educational lecture content — reasoning requires character tracking, not concept-building; no temporal IoU evaluation; no comparison of retrieval configurations (transcript-only vs. multimodal); no per-hop ground truth span annotations; structured event chains are hand-crafted rather than derived from a retrieval pipeline.</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>LongVidSearch: An Agentic Benchmark for Multi-hop Evidence Retrieval Planning in Long Videos</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.14468</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Introduces a benchmark of 3,000 questions across 447 long videos (avg 26 min) that enforces strict multi-hop evidence retrieval with 2-hop, 3-hop, and 4-hop configurations — removing any single clip makes the question unsolvable. Evaluates AI agents on iterative retrieval planning across four reasoning categories (State Mutation, Causal Inference, Global Summary, Visual Tracking); even GPT-5 achieves only 42.43% accuracy, identifying retrieval planning as the primary bottleneck.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>First benchmark to enforce strict per-hop retrieval necessity with explicit hop counts; agentic evaluation interface exposes planning failures invisible to single-pass models; broad reasoning categories; strong evidence that multi-hop retrieval is unsolved even for GPT-5.</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>General video content (not educational lectures); uses agentic tool-call retrieval rather than a transcript-chunk RAG pipeline; evaluates answer accuracy only — no temporal IoU or hit rate@k; no transcript or audio modality; no comparison of retrieval configurations; no per-hop ground truth time spans provided to the evaluator.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr">
         <is>
           <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
@@ -1631,119 +1631,82 @@
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>LongVidSearch: An Agentic Benchmark for Multi-hop Evidence Retrieval Planning in Long Videos</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2603.14468</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Introduces a benchmark of 3,000 questions across 447 long videos (avg 26 min) that enforces strict multi-hop evidence retrieval with 2-hop, 3-hop, and 4-hop configurations — removing any single clip makes the question unsolvable. Evaluates AI agents on iterative retrieval planning across four reasoning categories (State Mutation, Causal Inference, Global Summary, Visual Tracking); even GPT-5 achieves only 42.43% accuracy, identifying retrieval planning as the primary bottleneck.</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>First benchmark to enforce strict per-hop retrieval necessity with explicit hop counts; agentic evaluation interface exposes planning failures invisible to single-pass models; broad reasoning categories; strong evidence that multi-hop retrieval is unsolved even for GPT-5.</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>General video content (not educational lectures); uses agentic tool-call retrieval rather than a transcript-chunk RAG pipeline; evaluates answer accuracy only — no temporal IoU or hit rate@k; no transcript or audio modality; no comparison of retrieval configurations; no per-hop ground truth time spans provided to the evaluator.</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>EduVidQA: Generating and Evaluating Long-form Answers to Student Questions based on Lecture Videos</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.24120</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Presents EduVidQA, a dataset of 5,252 QA pairs from 296 CS lecture videos (ML, Algorithms, NLP, Deep Learning) spanning Bloom's taxonomy difficulty levels; includes timestamps for all questions and flags ~44% as visually dependent. Benchmarks six SOTA MLLMs, showing the task remains significantly challenging for current systems.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Closest domain match to this project (CS lecture videos, technical content); timestamps included; Bloom's taxonomy difficulty tagging; visual dependence flagging; real student questions used for 270 manually curated pairs.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>No RAG pipeline — uses a fixed 4-minute context window around each timestamp; no multi-hop questions or per-hop span annotations; no temporal IoU or hit rate@k evaluation; QA pairs are mostly synthetically generated (only 270/5252 manually curated); no comparison of retrieval configurations.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2025</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>EduVidQA: Generating and Evaluating Long-form Answers to Student Questions based on Lecture Videos</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.24120</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Presents EduVidQA, a dataset of 5,252 QA pairs from 296 CS lecture videos (ML, Algorithms, NLP, Deep Learning) spanning Bloom's taxonomy difficulty levels; includes timestamps for all questions and flags ~44% as visually dependent. Benchmarks six SOTA MLLMs, showing the task remains significantly challenging for current systems.</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Closest domain match to this project (CS lecture videos, technical content); timestamps included; Bloom's taxonomy difficulty tagging; visual dependence flagging; real student questions used for 270 manually curated pairs.</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>No RAG pipeline — uses a fixed 4-minute context window around each timestamp; no multi-hop questions or per-hop span annotations; no temporal IoU or hit rate@k evaluation; QA pairs are mostly synthetically generated (only 270/5252 manually curated); no comparison of retrieval configurations.</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Vgent: Graph-based Retrieval-Reasoning-Augmented Generation For Long Video Understanding</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2510.14032</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Proposes Vgent (NeurIPS 2025 Spotlight), a framework that represents video content as semantic relationship graphs over clips and adds an intermediate structured verification step to reduce retrieval noise in LVLMs. Achieves 3.0–5.4% improvement on MLVU and outperforms existing video RAG methods by 8.6%.</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Graph-based semantic structure captures relationships between clips beyond cosine similarity; structured verification reduces hallucination from noisy retrieval; NeurIPS 2025 Spotlight recognition; strong empirical gains over flat video RAG baselines.</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated on general video benchmarks (MLVU, not lecture domain); no temporal IoU evaluation; no multi-hop per-hop annotation; graph construction requires additional preprocessing overhead; no comparison of text-only vs. multimodal retrieval configurations.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>✓ EMNLP 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Vgent: Graph-based Retrieval-Reasoning-Augmented Generation For Long Video Understanding</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2510.14032</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Proposes Vgent (NeurIPS 2025 Spotlight), a framework that represents video content as semantic relationship graphs over clips and adds an intermediate structured verification step to reduce retrieval noise in LVLMs. Achieves 3.0–5.4% improvement on MLVU and outperforms existing video RAG methods by 8.6%.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Graph-based semantic structure captures relationships between clips beyond cosine similarity; structured verification reduces hallucination from noisy retrieval; NeurIPS 2025 Spotlight recognition; strong empirical gains over flat video RAG baselines.</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Evaluated on general video benchmarks (MLVU, not lecture domain); no temporal IoU evaluation; no multi-hop per-hop annotation; graph construction requires additional preprocessing overhead; no comparison of text-only vs. multimodal retrieval configurations.</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
           <t>✓ NeurIPS 2025 (Spotlight)</t>
         </is>
       </c>
     </row>
+    <row r="33" ht="40" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
